--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N54_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N54_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>5.978273165132395</v>
+        <v>0.9714693893340143</v>
       </c>
       <c r="D2" t="n">
-        <v>6.960816772648876</v>
+        <v>1.131132725555442</v>
       </c>
       <c r="E2" t="n">
-        <v>6.506087622474041</v>
+        <v>1.057239238652032</v>
       </c>
       <c r="F2" t="n">
-        <v>6.229534185379807</v>
+        <v>1.012299305124218</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>12.04533772339885</v>
+        <v>1.957367380052313</v>
       </c>
       <c r="D3" t="n">
-        <v>13.07359405760323</v>
+        <v>2.124459034360525</v>
       </c>
       <c r="E3" t="n">
-        <v>6.506087622474041</v>
+        <v>1.057239238652032</v>
       </c>
       <c r="F3" t="n">
-        <v>6.229534185379807</v>
+        <v>1.012299305124218</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.03265862022419</v>
+        <v>3.74280702578643</v>
       </c>
       <c r="D4" t="n">
-        <v>22.98550752046137</v>
+        <v>3.735144972074973</v>
       </c>
       <c r="E4" t="n">
-        <v>6.506087622474041</v>
+        <v>1.057239238652032</v>
       </c>
       <c r="F4" t="n">
-        <v>6.229534185379807</v>
+        <v>1.012299305124218</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>7.456348852487566</v>
+        <v>1.211656688529229</v>
       </c>
       <c r="D5" t="n">
-        <v>7.194483419514329</v>
+        <v>1.169103555671078</v>
       </c>
       <c r="E5" t="n">
-        <v>6.506087622474041</v>
+        <v>1.057239238652032</v>
       </c>
       <c r="F5" t="n">
-        <v>6.229534185379807</v>
+        <v>1.012299305124218</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>10.7588734838086</v>
+        <v>1.748316941118898</v>
       </c>
       <c r="D6" t="n">
-        <v>10.82404527927736</v>
+        <v>1.75890735788257</v>
       </c>
       <c r="E6" t="n">
-        <v>6.506087622474041</v>
+        <v>1.057239238652032</v>
       </c>
       <c r="F6" t="n">
-        <v>6.229534185379807</v>
+        <v>1.012299305124218</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>24.0746463640352</v>
+        <v>3.912130034155721</v>
       </c>
       <c r="D7" t="n">
-        <v>23.77341204036599</v>
+        <v>3.863179456559473</v>
       </c>
       <c r="E7" t="n">
-        <v>6.506087622474041</v>
+        <v>1.057239238652032</v>
       </c>
       <c r="F7" t="n">
-        <v>6.229534185379807</v>
+        <v>1.012299305124218</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>17.75639553051298</v>
+        <v>2.885414273708359</v>
       </c>
       <c r="D8" t="n">
-        <v>17.11948329257675</v>
+        <v>2.781916035043722</v>
       </c>
       <c r="E8" t="n">
-        <v>6.506087622474041</v>
+        <v>1.057239238652032</v>
       </c>
       <c r="F8" t="n">
-        <v>6.229534185379807</v>
+        <v>1.012299305124218</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>17.77568224110953</v>
+        <v>2.888548364180299</v>
       </c>
       <c r="D9" t="n">
-        <v>17.91745837397553</v>
+        <v>2.911586985771023</v>
       </c>
       <c r="E9" t="n">
-        <v>6.506087622474041</v>
+        <v>1.057239238652032</v>
       </c>
       <c r="F9" t="n">
-        <v>6.229534185379807</v>
+        <v>1.012299305124218</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>27.44872120892725</v>
+        <v>4.460417196450678</v>
       </c>
       <c r="D10" t="n">
-        <v>27.14038922844422</v>
+        <v>4.410313249622186</v>
       </c>
       <c r="E10" t="n">
-        <v>6.506087622474041</v>
+        <v>1.057239238652032</v>
       </c>
       <c r="F10" t="n">
-        <v>6.229534185379807</v>
+        <v>1.012299305124218</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>27.24438622674552</v>
+        <v>4.427212761846147</v>
       </c>
       <c r="D11" t="n">
-        <v>26.85279169530744</v>
+        <v>4.36357865048746</v>
       </c>
       <c r="E11" t="n">
-        <v>6.506087622474041</v>
+        <v>1.057239238652032</v>
       </c>
       <c r="F11" t="n">
-        <v>6.229534185379807</v>
+        <v>1.012299305124218</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>18.96103795672725</v>
+        <v>3.081168667968179</v>
       </c>
       <c r="D12" t="n">
-        <v>18.65964386004379</v>
+        <v>3.032192127257115</v>
       </c>
       <c r="E12" t="n">
-        <v>6.506087622474041</v>
+        <v>1.057239238652032</v>
       </c>
       <c r="F12" t="n">
-        <v>6.229534185379807</v>
+        <v>1.012299305124218</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>18.07257211362244</v>
+        <v>2.936792968463646</v>
       </c>
       <c r="D13" t="n">
-        <v>18.13902003501533</v>
+        <v>2.947590755689991</v>
       </c>
       <c r="E13" t="n">
-        <v>6.506087622474041</v>
+        <v>1.057239238652032</v>
       </c>
       <c r="F13" t="n">
-        <v>6.229534185379807</v>
+        <v>1.012299305124218</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>14.44543563041288</v>
+        <v>2.347383289942092</v>
       </c>
       <c r="D14" t="n">
-        <v>14.81696951591144</v>
+        <v>2.407757546335609</v>
       </c>
       <c r="E14" t="n">
-        <v>6.506087622474041</v>
+        <v>1.057239238652032</v>
       </c>
       <c r="F14" t="n">
-        <v>6.229534185379807</v>
+        <v>1.012299305124218</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>15.09849884605723</v>
+        <v>2.453506062484299</v>
       </c>
       <c r="D15" t="n">
-        <v>15.53007438861407</v>
+        <v>2.523637088149786</v>
       </c>
       <c r="E15" t="n">
-        <v>6.506087622474041</v>
+        <v>1.057239238652032</v>
       </c>
       <c r="F15" t="n">
-        <v>6.229534185379807</v>
+        <v>1.012299305124218</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
